--- a/05_Deploying/error_calc_u.xlsx
+++ b/05_Deploying/error_calc_u.xlsx
@@ -641,10 +641,10 @@
         <v>1.108391645487563</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2396112462249814</v>
+        <v>0.1849132239131551</v>
       </c>
       <c r="E9" t="n">
-        <v>94.8503002811803</v>
+        <v>0.6233453068932223</v>
       </c>
       <c r="F9" t="n">
         <v>0.1567489020838251</v>

--- a/05_Deploying/error_calc_u.xlsx
+++ b/05_Deploying/error_calc_u.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,301 +531,626 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2D-2</t>
+          <t>2D-1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2080976789810932</v>
+        <v>78.84532094165768</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4748882306491556</v>
+        <v>24.84965344717872</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2485919105210732</v>
+        <v>51.64870711517319</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9907418708814486</v>
+        <v>20.40552440207702</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2597723728107033</v>
+        <v>98.84121261440849</v>
       </c>
       <c r="G5" t="n">
-        <v>1.089674204076753</v>
+        <v>22.97981497986851</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2D-3</t>
+          <t>2D-2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01908396706523412</v>
+        <v>0.2080976789810932</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1777560993885995</v>
+        <v>0.4748882306491556</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01327951951226631</v>
+        <v>0.2485919105210732</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07002099625979734</v>
+        <v>0.9907418708814486</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02031047561539842</v>
+        <v>0.2597723728107033</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0949661161855217</v>
+        <v>1.089674204076753</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2D-4</t>
+          <t>2D-2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8178798363800699</v>
+        <v>0.01685375903886461</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004501782550566229</v>
+        <v>24.84965345289379</v>
       </c>
       <c r="D7" t="n">
-        <v>1.064915836135828</v>
+        <v>0.01685211234988592</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001783026669228782</v>
+        <v>19.91634389852649</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6218487303274971</v>
+        <v>0.0168528246082826</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00266459745506085</v>
+        <v>22.13101982324122</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2D-5</t>
+          <t>2D-3</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2442751888592871</v>
+        <v>0.01908396706523412</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00370304746735338</v>
+        <v>0.1777560993885995</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2017466979515206</v>
+        <v>0.01327951951226631</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003637668531925886</v>
+        <v>0.07002099625979734</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2029921081125283</v>
+        <v>0.02031047561539842</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003774117340132525</v>
+        <v>0.0949661161855217</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2D-1C</t>
+          <t>2D-3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6336430186466043</v>
+        <v>0.01701226628355944</v>
       </c>
       <c r="C9" t="n">
-        <v>1.108391645487563</v>
+        <v>13.06546516128071</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1849132239131551</v>
+        <v>0.01701081662242726</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6233453068932223</v>
+        <v>9.445935707672184</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1567489020838251</v>
+        <v>0.01701227294419025</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1256745165019006</v>
+        <v>10.85585051751327</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2D-2C</t>
+          <t>2D-4</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.460558769034979</v>
+        <v>0.8178798363800699</v>
       </c>
       <c r="C10" t="n">
-        <v>0.005534936225986076</v>
+        <v>0.004501782550566229</v>
       </c>
       <c r="D10" t="n">
-        <v>1.000400629445321</v>
+        <v>1.064915836135828</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00397934674647056</v>
+        <v>0.001783026669228782</v>
       </c>
       <c r="F10" t="n">
-        <v>0.808050321941583</v>
+        <v>0.6218487303274971</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00509314069443814</v>
+        <v>0.00266459745506085</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2D-3C</t>
+          <t>2D-4</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7.360396744669779</v>
+        <v>24.84965344851316</v>
       </c>
       <c r="C11" t="n">
-        <v>4.296064129869867</v>
+        <v>0.01685375215373821</v>
       </c>
       <c r="D11" t="n">
-        <v>4.864436933152143</v>
+        <v>24.84965344820012</v>
       </c>
       <c r="E11" t="n">
-        <v>4.285164124634501</v>
+        <v>0.01710027453255537</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7064620106350208</v>
+        <v>24.84965344915163</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2637920643944852</v>
+        <v>0.01638146070722372</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2D-4C</t>
+          <t>2D-5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1568447548049704</v>
+        <v>0.2442751888592871</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0447226092986776</v>
+        <v>0.00370304746735338</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08977591016033129</v>
+        <v>0.2017466979515206</v>
       </c>
       <c r="E12" t="n">
-        <v>15.08900523633907</v>
+        <v>0.003637668531925886</v>
       </c>
       <c r="F12" t="n">
-        <v>3.00457430605424</v>
+        <v>0.2029921081125283</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02212724294794008</v>
+        <v>0.003774117340132525</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2D-5C</t>
+          <t>2D-5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7327215078774588</v>
+        <v>13.06546515040171</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1848303499203529</v>
+        <v>0.01700945664451564</v>
       </c>
       <c r="D13" t="n">
-        <v>22.30630633975876</v>
+        <v>13.06546515040161</v>
       </c>
       <c r="E13" t="n">
-        <v>5.224900659725787</v>
+        <v>0.01726051828477532</v>
       </c>
       <c r="F13" t="n">
-        <v>0.452616541704891</v>
+        <v>13.06546515040243</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1256361069677607</v>
+        <v>0.0165286472814112</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2D-6C</t>
+          <t>2D-1C</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6026691109258315</v>
+        <v>0.6336430186466043</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1657180429210559</v>
+        <v>1.108391645487563</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5681341934352773</v>
+        <v>0.1849132239131551</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2372343127299034</v>
+        <v>0.6233453068932223</v>
       </c>
       <c r="F14" t="n">
-        <v>1.020100839211576</v>
+        <v>0.1567489020838251</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2023870953787081</v>
+        <v>0.1256745165019006</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>2D-7C</t>
+          <t>2D-1C</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1146163099624452</v>
+        <v>24.84676605752531</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05786544005727153</v>
+        <v>24.84676607049084</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1417631825138495</v>
+        <v>9.134926171104125</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1194929871545562</v>
+        <v>19.91417908861606</v>
       </c>
       <c r="F15" t="n">
-        <v>0.07363728299718508</v>
+        <v>10.59833366665727</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05400593946795938</v>
+        <v>7.075045285029394</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t>2D-2C</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.460558769034979</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.005534936225986076</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.000400629445321</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.00397934674647056</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.808050321941583</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.00509314069443814</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2D-2C</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>24.84965344858122</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.847923628677561</v>
+      </c>
+      <c r="D17" t="n">
+        <v>22.62675873562025</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8535076957458964</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24.84965344921965</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8208164200633019</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2D-3C</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7.360396744669779</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.296064129869867</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.864436933152143</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.285164124634501</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.7064620106350208</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2637920643944852</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>2D-3C</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>84.20400294629881</v>
+      </c>
+      <c r="C19" t="n">
+        <v>50.93091155989302</v>
+      </c>
+      <c r="D19" t="n">
+        <v>70.37058110477626</v>
+      </c>
+      <c r="E19" t="n">
+        <v>54.23800237123512</v>
+      </c>
+      <c r="F19" t="n">
+        <v>68.84414842706035</v>
+      </c>
+      <c r="G19" t="n">
+        <v>28.07763170574724</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>2D-4C</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.1568447548049704</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0447226092986776</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.08977591016033129</v>
+      </c>
+      <c r="E20" t="n">
+        <v>15.08900523633907</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.00457430605424</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.02212724294794008</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2D-4C</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>13.06546514566589</v>
+      </c>
+      <c r="C21" t="n">
+        <v>13.06546519061384</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11.8255477356972</v>
+      </c>
+      <c r="E21" t="n">
+        <v>49.81444727363622</v>
+      </c>
+      <c r="F21" t="n">
+        <v>21.4816122584932</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10.71567062009841</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>2D-5C</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.7327215078774588</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.1848303499203529</v>
+      </c>
+      <c r="D22" t="n">
+        <v>22.30630633975876</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.224900659725787</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.452616541704891</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1256361069677607</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>2D-5C</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>48.54064649819699</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10.50057247278703</v>
+      </c>
+      <c r="D23" t="n">
+        <v>57.92135021448396</v>
+      </c>
+      <c r="E23" t="n">
+        <v>14.79627155854481</v>
+      </c>
+      <c r="F23" t="n">
+        <v>37.14126138024387</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7.037912814069137</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>2D-6C</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.6026691109258315</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1657180429210559</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5681341934352773</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.2372343127299034</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.020100839211576</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.2023870953787081</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2D-6C</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>46.06269745576095</v>
+      </c>
+      <c r="C25" t="n">
+        <v>14.55394424278017</v>
+      </c>
+      <c r="D25" t="n">
+        <v>57.89807972384955</v>
+      </c>
+      <c r="E25" t="n">
+        <v>24.2968036645717</v>
+      </c>
+      <c r="F25" t="n">
+        <v>60.8062476698205</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12.74660883483075</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2D-7C</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1146163099624452</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.05786544005727153</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1417631825138495</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1194929871545562</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.07363728299718508</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05400593946795938</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>2D-7C</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>18.75395340392871</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.10893170803663</v>
+      </c>
+      <c r="D27" t="n">
+        <v>18.59206327792254</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.270819548620477</v>
+      </c>
+      <c r="F27" t="n">
+        <v>19.01978331071836</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.8802859951212549</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
           <t>2D-8C</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B28" t="n">
         <v>7.948258225245979</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C28" t="n">
         <v>0.5107103192572942</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D28" t="n">
         <v>5.653448873674128</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E28" t="n">
         <v>0.5067542725161995</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F28" t="n">
         <v>24.1621071275993</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G28" t="n">
         <v>0.767461505185156</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>2D-8C</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>114.1908815919339</v>
+      </c>
+      <c r="C29" t="n">
+        <v>9.998415981837123</v>
+      </c>
+      <c r="D29" t="n">
+        <v>110.3188942230593</v>
+      </c>
+      <c r="E29" t="n">
+        <v>11.67488358905882</v>
+      </c>
+      <c r="F29" t="n">
+        <v>193.3138437840726</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10.51242027125691</v>
       </c>
     </row>
   </sheetData>
